--- a/SGC-CKN/Excel/2aa1b188-7ab9-4e17-ae8d-75789dd481a7_Thanh_Hoá_P1_101_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/2aa1b188-7ab9-4e17-ae8d-75789dd481a7_Thanh_Hoá_P1_101_D800_08-04-2026.xlsx
@@ -1148,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.15</v>
@@ -1157,10 +1157,10 @@
         <v>0.12</v>
       </c>
       <c r="I11" s="5">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="J11" s="8">
-        <v>5.14</v>
+        <v>9.86</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1221,16 +1221,16 @@
         <v>-4.25</v>
       </c>
       <c r="G13" s="12">
-        <v>-7.55</v>
+        <v>-7.35</v>
       </c>
       <c r="H13" s="12">
         <v>0.4</v>
       </c>
       <c r="I13" s="12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J13" s="8">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>34</v>
@@ -1253,7 +1253,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="15">
-        <v>-7.55</v>
+        <v>-7.35</v>
       </c>
       <c r="G14" s="15">
         <v>-16.35</v>
@@ -1262,10 +1262,10 @@
         <v>0.8</v>
       </c>
       <c r="I14" s="15">
-        <v>8.8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="8">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>34</v>
@@ -1326,16 +1326,16 @@
         <v>-21.35</v>
       </c>
       <c r="G16" s="21">
-        <v>-24.55</v>
+        <v>-25.55</v>
       </c>
       <c r="H16" s="21">
         <v>0.45</v>
       </c>
       <c r="I16" s="21">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J16" s="8">
-        <v>7.11</v>
+        <v>9.33</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>34</v>
@@ -1358,7 +1358,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="24">
-        <v>-24.55</v>
+        <v>-25.55</v>
       </c>
       <c r="G17" s="24">
         <v>-39.1</v>
@@ -1367,10 +1367,10 @@
         <v>1.82</v>
       </c>
       <c r="I17" s="24">
-        <v>14.55</v>
+        <v>13.55</v>
       </c>
       <c r="J17" s="8">
-        <v>8.01</v>
+        <v>7.46</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>34</v>
@@ -1560,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.15</v>
@@ -1569,10 +1569,10 @@
         <v>0.12</v>
       </c>
       <c r="H2" s="5">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="I2" s="8">
-        <v>5.14</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1621,16 +1621,16 @@
         <v>-4.25</v>
       </c>
       <c r="F4" s="12">
-        <v>-7.55</v>
+        <v>-7.35</v>
       </c>
       <c r="G4" s="12">
         <v>0.4</v>
       </c>
       <c r="H4" s="12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I4" s="8">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1647,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-7.55</v>
+        <v>-7.35</v>
       </c>
       <c r="F5" s="15">
         <v>-16.35</v>
@@ -1656,10 +1656,10 @@
         <v>0.8</v>
       </c>
       <c r="H5" s="15">
-        <v>8.8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="8">
-        <v>11</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,16 +1708,16 @@
         <v>-21.35</v>
       </c>
       <c r="F7" s="21">
-        <v>-24.55</v>
+        <v>-25.55</v>
       </c>
       <c r="G7" s="21">
         <v>0.45</v>
       </c>
       <c r="H7" s="21">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="8">
-        <v>7.11</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-24.55</v>
+        <v>-25.55</v>
       </c>
       <c r="F8" s="24">
         <v>-39.1</v>
@@ -1743,10 +1743,10 @@
         <v>1.82</v>
       </c>
       <c r="H8" s="24">
-        <v>14.55</v>
+        <v>13.55</v>
       </c>
       <c r="I8" s="8">
-        <v>8.01</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.27</v>
@@ -1801,10 +1801,10 @@
         <v>9.22</v>
       </c>
       <c r="H10" s="33">
-        <v>43.72</v>
+        <v>44.27</v>
       </c>
       <c r="I10" s="33">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>
